--- a/Compititor's_Price/Recticel_Prices/Recticel_Prices_09-09-2025.xlsx
+++ b/Compititor's_Price/Recticel_Prices/Recticel_Prices_09-09-2025.xlsx
@@ -538,17 +538,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>£10.98</t>
+          <t>£10.95</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>£10.98</t>
+          <t>£10.95</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>£10.98</t>
+          <t>£10.95</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -659,17 +659,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>£12.33</t>
+          <t>£12.30</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>£12.33</t>
+          <t>£12.30</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>£12.33</t>
+          <t>£12.30</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1022,17 +1022,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>£21.00</t>
+          <t>£20.59</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>£21.00</t>
+          <t>£20.59</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>£21.00</t>
+          <t>£20.59</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>£21.05</t>
+          <t>POA or OOS</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>£35.9</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1385,17 +1385,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>£26.40</t>
+          <t>£25.79</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>£26.40</t>
+          <t>£25.79</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>£26.40</t>
+          <t>£25.79</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1627,39 +1627,39 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>£28.00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>£28.00</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>£28.00</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>£30.00-Sale Price old price: £35.95</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>POA or OOS</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>£27.44</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
           <t>£28.35</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>£28.35</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>£28.35</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>£30.00-Sale Price old price: £35.95</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>POA or OOS</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>£27.44</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>£28.35</t>
-        </is>
-      </c>
       <c r="J11" t="inlineStr">
         <is>
           <t>£29.16 presale price: £46.38</t>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>£27.48</t>
+          <t>£26.87</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>£36.50</t>
+          <t>£36.30</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>£36.50</t>
+          <t>£36.30</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1990,12 +1990,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>£42.50</t>
+          <t>£41.09</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>£42.50</t>
+          <t>£41.09</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>£43.99</t>
+          <t>£42.00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>£43.99</t>
+          <t>£42.00</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
